--- a/docs/test-plans/qapulse-negative-tests.xlsx
+++ b/docs/test-plans/qapulse-negative-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4073,7 +4073,11 @@
       </c>
       <c r="J2" s="177" t="inlineStr"/>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr"/>
+      <c r="L2" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:15</t>
+        </is>
+      </c>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4120,7 +4124,11 @@
       </c>
       <c r="J3" s="177" t="inlineStr"/>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr"/>
+      <c r="L3" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:20</t>
+        </is>
+      </c>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4167,7 +4175,11 @@
       </c>
       <c r="J4" s="177" t="inlineStr"/>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr"/>
+      <c r="L4" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:33</t>
+        </is>
+      </c>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4214,7 +4226,11 @@
       </c>
       <c r="J5" s="177" t="inlineStr"/>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:40</t>
+        </is>
+      </c>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4262,7 +4278,11 @@
       </c>
       <c r="J6" s="177" t="inlineStr"/>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr"/>
+      <c r="L6" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:48</t>
+        </is>
+      </c>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4309,7 +4329,11 @@
       </c>
       <c r="J7" s="177" t="inlineStr"/>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr"/>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:56</t>
+        </is>
+      </c>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4356,7 +4380,11 @@
       </c>
       <c r="J8" s="177" t="inlineStr"/>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr"/>
+      <c r="L8" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:71</t>
+        </is>
+      </c>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4403,7 +4431,11 @@
       </c>
       <c r="J9" s="177" t="inlineStr"/>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr"/>
+      <c r="L9" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:86</t>
+        </is>
+      </c>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4450,7 +4482,11 @@
       </c>
       <c r="J10" s="177" t="inlineStr"/>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr"/>
+      <c r="L10" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:96</t>
+        </is>
+      </c>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4497,7 +4533,11 @@
       </c>
       <c r="J11" s="177" t="inlineStr"/>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr"/>
+      <c r="L11" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:103</t>
+        </is>
+      </c>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4544,7 +4584,11 @@
       </c>
       <c r="J12" s="177" t="inlineStr"/>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr"/>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:108</t>
+        </is>
+      </c>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4591,7 +4635,11 @@
       </c>
       <c r="J13" s="177" t="inlineStr"/>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr"/>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:119</t>
+        </is>
+      </c>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4638,7 +4686,11 @@
       </c>
       <c r="J14" s="177" t="inlineStr"/>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr"/>
+      <c r="L14" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:127</t>
+        </is>
+      </c>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4685,7 +4737,11 @@
       </c>
       <c r="J15" s="177" t="inlineStr"/>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr"/>
+      <c r="L15" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:135</t>
+        </is>
+      </c>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4732,7 +4788,11 @@
       </c>
       <c r="J16" s="177" t="inlineStr"/>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr"/>
+      <c r="L16" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:143</t>
+        </is>
+      </c>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4779,7 +4839,11 @@
       </c>
       <c r="J17" s="177" t="inlineStr"/>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr"/>
+      <c r="L17" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:158</t>
+        </is>
+      </c>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4826,7 +4890,11 @@
       </c>
       <c r="J18" s="177" t="inlineStr"/>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr"/>
+      <c r="L18" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:167</t>
+        </is>
+      </c>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4873,7 +4941,11 @@
       </c>
       <c r="J19" s="177" t="inlineStr"/>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr"/>
+      <c r="L19" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:178</t>
+        </is>
+      </c>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4920,7 +4992,11 @@
       </c>
       <c r="J20" s="177" t="inlineStr"/>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr"/>
+      <c r="L20" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:195</t>
+        </is>
+      </c>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4967,7 +5043,11 @@
       </c>
       <c r="J21" s="177" t="inlineStr"/>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr"/>
+      <c r="L21" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:216</t>
+        </is>
+      </c>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5014,7 +5094,11 @@
       </c>
       <c r="J22" s="177" t="inlineStr"/>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr"/>
+      <c r="L22" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:230</t>
+        </is>
+      </c>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5061,7 +5145,11 @@
       </c>
       <c r="J23" s="177" t="inlineStr"/>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr"/>
+      <c r="L23" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:237</t>
+        </is>
+      </c>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5108,7 +5196,11 @@
       </c>
       <c r="J24" s="177" t="inlineStr"/>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr"/>
+      <c r="L24" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:244</t>
+        </is>
+      </c>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5155,7 +5247,11 @@
       </c>
       <c r="J25" s="177" t="inlineStr"/>
       <c r="K25" s="177" t="inlineStr"/>
-      <c r="L25" s="177" t="inlineStr"/>
+      <c r="L25" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:259</t>
+        </is>
+      </c>
       <c r="M25" s="177" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5202,7 +5298,11 @@
       </c>
       <c r="J26" s="177" t="inlineStr"/>
       <c r="K26" s="177" t="inlineStr"/>
-      <c r="L26" s="177" t="inlineStr"/>
+      <c r="L26" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:265</t>
+        </is>
+      </c>
       <c r="M26" s="177" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5249,7 +5349,11 @@
       </c>
       <c r="J27" s="177" t="inlineStr"/>
       <c r="K27" s="177" t="inlineStr"/>
-      <c r="L27" s="177" t="inlineStr"/>
+      <c r="L27" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:276</t>
+        </is>
+      </c>
       <c r="M27" s="177" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5296,7 +5400,11 @@
       </c>
       <c r="J28" s="177" t="inlineStr"/>
       <c r="K28" s="177" t="inlineStr"/>
-      <c r="L28" s="177" t="inlineStr"/>
+      <c r="L28" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:286</t>
+        </is>
+      </c>
       <c r="M28" s="177" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5344,7 +5452,11 @@
       </c>
       <c r="J29" s="177" t="inlineStr"/>
       <c r="K29" s="177" t="inlineStr"/>
-      <c r="L29" s="177" t="inlineStr"/>
+      <c r="L29" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:297</t>
+        </is>
+      </c>
       <c r="M29" s="177" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5391,7 +5503,11 @@
       </c>
       <c r="J30" s="177" t="inlineStr"/>
       <c r="K30" s="177" t="inlineStr"/>
-      <c r="L30" s="177" t="inlineStr"/>
+      <c r="L30" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:316</t>
+        </is>
+      </c>
       <c r="M30" s="177" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5438,7 +5554,11 @@
       </c>
       <c r="J31" s="177" t="inlineStr"/>
       <c r="K31" s="177" t="inlineStr"/>
-      <c r="L31" s="177" t="inlineStr"/>
+      <c r="L31" s="177" t="inlineStr">
+        <is>
+          <t>Fixme (blocked) — artifacts/qa-automation/tests/negative.spec.ts:358</t>
+        </is>
+      </c>
       <c r="M31" s="177" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5486,7 +5606,11 @@
       </c>
       <c r="J32" s="177" t="inlineStr"/>
       <c r="K32" s="177" t="inlineStr"/>
-      <c r="L32" s="177" t="inlineStr"/>
+      <c r="L32" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:364</t>
+        </is>
+      </c>
       <c r="M32" s="177" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5533,7 +5657,11 @@
       </c>
       <c r="J33" s="177" t="inlineStr"/>
       <c r="K33" s="177" t="inlineStr"/>
-      <c r="L33" s="177" t="inlineStr"/>
+      <c r="L33" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:373</t>
+        </is>
+      </c>
       <c r="M33" s="177" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5581,7 +5709,11 @@
       </c>
       <c r="J34" s="177" t="inlineStr"/>
       <c r="K34" s="177" t="inlineStr"/>
-      <c r="L34" s="177" t="inlineStr"/>
+      <c r="L34" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:383</t>
+        </is>
+      </c>
       <c r="M34" s="177" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5628,7 +5760,11 @@
       </c>
       <c r="J35" s="177" t="inlineStr"/>
       <c r="K35" s="177" t="inlineStr"/>
-      <c r="L35" s="177" t="inlineStr"/>
+      <c r="L35" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:396</t>
+        </is>
+      </c>
       <c r="M35" s="177" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5676,7 +5812,11 @@
       </c>
       <c r="J36" s="177" t="inlineStr"/>
       <c r="K36" s="177" t="inlineStr"/>
-      <c r="L36" s="177" t="inlineStr"/>
+      <c r="L36" s="177" t="inlineStr">
+        <is>
+          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:420</t>
+        </is>
+      </c>
       <c r="M36" s="177" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/test-plans/qapulse-negative-tests.xlsx
+++ b/docs/test-plans/qapulse-negative-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t>None</a:t>
+                <a:t/>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4073,11 +4073,7 @@
       </c>
       <c r="J2" s="177" t="inlineStr"/>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:15</t>
-        </is>
-      </c>
+      <c r="L2" s="177" t="inlineStr"/>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4124,11 +4120,7 @@
       </c>
       <c r="J3" s="177" t="inlineStr"/>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:20</t>
-        </is>
-      </c>
+      <c r="L3" s="177" t="inlineStr"/>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4175,11 +4167,7 @@
       </c>
       <c r="J4" s="177" t="inlineStr"/>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:33</t>
-        </is>
-      </c>
+      <c r="L4" s="177" t="inlineStr"/>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4226,11 +4214,7 @@
       </c>
       <c r="J5" s="177" t="inlineStr"/>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:40</t>
-        </is>
-      </c>
+      <c r="L5" s="177" t="inlineStr"/>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4278,11 +4262,7 @@
       </c>
       <c r="J6" s="177" t="inlineStr"/>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:48</t>
-        </is>
-      </c>
+      <c r="L6" s="177" t="inlineStr"/>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4329,11 +4309,7 @@
       </c>
       <c r="J7" s="177" t="inlineStr"/>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:56</t>
-        </is>
-      </c>
+      <c r="L7" s="177" t="inlineStr"/>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4380,11 +4356,7 @@
       </c>
       <c r="J8" s="177" t="inlineStr"/>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:71</t>
-        </is>
-      </c>
+      <c r="L8" s="177" t="inlineStr"/>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4431,11 +4403,7 @@
       </c>
       <c r="J9" s="177" t="inlineStr"/>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:86</t>
-        </is>
-      </c>
+      <c r="L9" s="177" t="inlineStr"/>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4482,11 +4450,7 @@
       </c>
       <c r="J10" s="177" t="inlineStr"/>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:96</t>
-        </is>
-      </c>
+      <c r="L10" s="177" t="inlineStr"/>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4533,11 +4497,7 @@
       </c>
       <c r="J11" s="177" t="inlineStr"/>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:103</t>
-        </is>
-      </c>
+      <c r="L11" s="177" t="inlineStr"/>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4584,11 +4544,7 @@
       </c>
       <c r="J12" s="177" t="inlineStr"/>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:108</t>
-        </is>
-      </c>
+      <c r="L12" s="177" t="inlineStr"/>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4635,11 +4591,7 @@
       </c>
       <c r="J13" s="177" t="inlineStr"/>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:119</t>
-        </is>
-      </c>
+      <c r="L13" s="177" t="inlineStr"/>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4686,11 +4638,7 @@
       </c>
       <c r="J14" s="177" t="inlineStr"/>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:127</t>
-        </is>
-      </c>
+      <c r="L14" s="177" t="inlineStr"/>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4737,11 +4685,7 @@
       </c>
       <c r="J15" s="177" t="inlineStr"/>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:135</t>
-        </is>
-      </c>
+      <c r="L15" s="177" t="inlineStr"/>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4788,11 +4732,7 @@
       </c>
       <c r="J16" s="177" t="inlineStr"/>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:143</t>
-        </is>
-      </c>
+      <c r="L16" s="177" t="inlineStr"/>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4839,11 +4779,7 @@
       </c>
       <c r="J17" s="177" t="inlineStr"/>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:158</t>
-        </is>
-      </c>
+      <c r="L17" s="177" t="inlineStr"/>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4890,11 +4826,7 @@
       </c>
       <c r="J18" s="177" t="inlineStr"/>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:167</t>
-        </is>
-      </c>
+      <c r="L18" s="177" t="inlineStr"/>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4941,11 +4873,7 @@
       </c>
       <c r="J19" s="177" t="inlineStr"/>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:178</t>
-        </is>
-      </c>
+      <c r="L19" s="177" t="inlineStr"/>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4992,11 +4920,7 @@
       </c>
       <c r="J20" s="177" t="inlineStr"/>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:195</t>
-        </is>
-      </c>
+      <c r="L20" s="177" t="inlineStr"/>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -5043,11 +4967,7 @@
       </c>
       <c r="J21" s="177" t="inlineStr"/>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:216</t>
-        </is>
-      </c>
+      <c r="L21" s="177" t="inlineStr"/>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5094,11 +5014,7 @@
       </c>
       <c r="J22" s="177" t="inlineStr"/>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:230</t>
-        </is>
-      </c>
+      <c r="L22" s="177" t="inlineStr"/>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5145,11 +5061,7 @@
       </c>
       <c r="J23" s="177" t="inlineStr"/>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:237</t>
-        </is>
-      </c>
+      <c r="L23" s="177" t="inlineStr"/>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5196,11 +5108,7 @@
       </c>
       <c r="J24" s="177" t="inlineStr"/>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:244</t>
-        </is>
-      </c>
+      <c r="L24" s="177" t="inlineStr"/>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5247,11 +5155,7 @@
       </c>
       <c r="J25" s="177" t="inlineStr"/>
       <c r="K25" s="177" t="inlineStr"/>
-      <c r="L25" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:259</t>
-        </is>
-      </c>
+      <c r="L25" s="177" t="inlineStr"/>
       <c r="M25" s="177" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5298,11 +5202,7 @@
       </c>
       <c r="J26" s="177" t="inlineStr"/>
       <c r="K26" s="177" t="inlineStr"/>
-      <c r="L26" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:265</t>
-        </is>
-      </c>
+      <c r="L26" s="177" t="inlineStr"/>
       <c r="M26" s="177" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5349,11 +5249,7 @@
       </c>
       <c r="J27" s="177" t="inlineStr"/>
       <c r="K27" s="177" t="inlineStr"/>
-      <c r="L27" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:276</t>
-        </is>
-      </c>
+      <c r="L27" s="177" t="inlineStr"/>
       <c r="M27" s="177" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5400,11 +5296,7 @@
       </c>
       <c r="J28" s="177" t="inlineStr"/>
       <c r="K28" s="177" t="inlineStr"/>
-      <c r="L28" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:286</t>
-        </is>
-      </c>
+      <c r="L28" s="177" t="inlineStr"/>
       <c r="M28" s="177" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5452,11 +5344,7 @@
       </c>
       <c r="J29" s="177" t="inlineStr"/>
       <c r="K29" s="177" t="inlineStr"/>
-      <c r="L29" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:297</t>
-        </is>
-      </c>
+      <c r="L29" s="177" t="inlineStr"/>
       <c r="M29" s="177" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5503,11 +5391,7 @@
       </c>
       <c r="J30" s="177" t="inlineStr"/>
       <c r="K30" s="177" t="inlineStr"/>
-      <c r="L30" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:316</t>
-        </is>
-      </c>
+      <c r="L30" s="177" t="inlineStr"/>
       <c r="M30" s="177" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5554,11 +5438,7 @@
       </c>
       <c r="J31" s="177" t="inlineStr"/>
       <c r="K31" s="177" t="inlineStr"/>
-      <c r="L31" s="177" t="inlineStr">
-        <is>
-          <t>Fixme (blocked) — artifacts/qa-automation/tests/negative.spec.ts:358</t>
-        </is>
-      </c>
+      <c r="L31" s="177" t="inlineStr"/>
       <c r="M31" s="177" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5606,11 +5486,7 @@
       </c>
       <c r="J32" s="177" t="inlineStr"/>
       <c r="K32" s="177" t="inlineStr"/>
-      <c r="L32" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:364</t>
-        </is>
-      </c>
+      <c r="L32" s="177" t="inlineStr"/>
       <c r="M32" s="177" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5657,11 +5533,7 @@
       </c>
       <c r="J33" s="177" t="inlineStr"/>
       <c r="K33" s="177" t="inlineStr"/>
-      <c r="L33" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:373</t>
-        </is>
-      </c>
+      <c r="L33" s="177" t="inlineStr"/>
       <c r="M33" s="177" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5709,11 +5581,7 @@
       </c>
       <c r="J34" s="177" t="inlineStr"/>
       <c r="K34" s="177" t="inlineStr"/>
-      <c r="L34" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:383</t>
-        </is>
-      </c>
+      <c r="L34" s="177" t="inlineStr"/>
       <c r="M34" s="177" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5760,11 +5628,7 @@
       </c>
       <c r="J35" s="177" t="inlineStr"/>
       <c r="K35" s="177" t="inlineStr"/>
-      <c r="L35" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:396</t>
-        </is>
-      </c>
+      <c r="L35" s="177" t="inlineStr"/>
       <c r="M35" s="177" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5812,11 +5676,7 @@
       </c>
       <c r="J36" s="177" t="inlineStr"/>
       <c r="K36" s="177" t="inlineStr"/>
-      <c r="L36" s="177" t="inlineStr">
-        <is>
-          <t>Automated — artifacts/qa-automation/tests/negative.spec.ts:420</t>
-        </is>
-      </c>
+      <c r="L36" s="177" t="inlineStr"/>
       <c r="M36" s="177" t="inlineStr"/>
     </row>
   </sheetData>

--- a/docs/test-plans/qapulse-negative-tests.xlsx
+++ b/docs/test-plans/qapulse-negative-tests.xlsx
@@ -1844,7 +1844,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
@@ -2190,7 +2190,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2267,7 +2267,7 @@
                 </a:defRPr>
               </a:pPr>
               <a:r>
-                <a:t/>
+                <a:t>None</a:t>
               </a:r>
               <a:endParaRPr lang="en-US"/>
             </a:p>
@@ -2300,7 +2300,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2404,7 +2404,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -2458,7 +2458,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="en-US"/>
         </a:p>
@@ -4071,9 +4071,17 @@
           <t>Validation error; no request/token</t>
         </is>
       </c>
-      <c r="J2" s="177" t="inlineStr"/>
+      <c r="J2" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K2" s="177" t="inlineStr"/>
-      <c r="L2" s="177" t="inlineStr"/>
+      <c r="L2" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.4s)</t>
+        </is>
+      </c>
       <c r="M2" s="177" t="inlineStr"/>
     </row>
     <row r="3">
@@ -4118,9 +4126,17 @@
           <t>Login denied</t>
         </is>
       </c>
-      <c r="J3" s="177" t="inlineStr"/>
+      <c r="J3" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K3" s="177" t="inlineStr"/>
-      <c r="L3" s="177" t="inlineStr"/>
+      <c r="L3" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (1.1s)</t>
+        </is>
+      </c>
       <c r="M3" s="177" t="inlineStr"/>
     </row>
     <row r="4">
@@ -4165,9 +4181,17 @@
           <t>401 -&gt; session cleared -&gt; redirect to /login</t>
         </is>
       </c>
-      <c r="J4" s="177" t="inlineStr"/>
+      <c r="J4" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K4" s="177" t="inlineStr"/>
-      <c r="L4" s="177" t="inlineStr"/>
+      <c r="L4" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M4" s="177" t="inlineStr"/>
     </row>
     <row r="5">
@@ -4212,9 +4236,17 @@
           <t>Redirected to /dashboard (reachable) - no blank screen</t>
         </is>
       </c>
-      <c r="J5" s="177" t="inlineStr"/>
+      <c r="J5" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K5" s="177" t="inlineStr"/>
-      <c r="L5" s="177" t="inlineStr"/>
+      <c r="L5" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (28.9s) || Last automated run: 2026-07-19 03:22 UTC — Passed (31.0s)</t>
+        </is>
+      </c>
       <c r="M5" s="177" t="inlineStr"/>
     </row>
     <row r="6">
@@ -4260,9 +4292,17 @@
           <t>Module-B records not listed; direct access denied/empty</t>
         </is>
       </c>
-      <c r="J6" s="177" t="inlineStr"/>
+      <c r="J6" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K6" s="177" t="inlineStr"/>
-      <c r="L6" s="177" t="inlineStr"/>
+      <c r="L6" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (1.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (1.2s)</t>
+        </is>
+      </c>
       <c r="M6" s="177" t="inlineStr"/>
     </row>
     <row r="7">
@@ -4307,9 +4347,17 @@
           <t>403 Access denied (no leak)</t>
         </is>
       </c>
-      <c r="J7" s="177" t="inlineStr"/>
+      <c r="J7" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K7" s="177" t="inlineStr"/>
-      <c r="L7" s="177" t="inlineStr"/>
+      <c r="L7" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.9s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.8s)</t>
+        </is>
+      </c>
       <c r="M7" s="177" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4354,9 +4402,17 @@
           <t>401 on every endpoint</t>
         </is>
       </c>
-      <c r="J8" s="177" t="inlineStr"/>
+      <c r="J8" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K8" s="177" t="inlineStr"/>
-      <c r="L8" s="177" t="inlineStr"/>
+      <c r="L8" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M8" s="177" t="inlineStr"/>
     </row>
     <row r="9">
@@ -4401,9 +4457,17 @@
           <t>403 (or 401) - no admin account minted</t>
         </is>
       </c>
-      <c r="J9" s="177" t="inlineStr"/>
+      <c r="J9" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K9" s="177" t="inlineStr"/>
-      <c r="L9" s="177" t="inlineStr"/>
+      <c r="L9" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M9" s="177" t="inlineStr"/>
     </row>
     <row r="10">
@@ -4448,9 +4512,17 @@
           <t>403 - role change is admin-only</t>
         </is>
       </c>
-      <c r="J10" s="177" t="inlineStr"/>
+      <c r="J10" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K10" s="177" t="inlineStr"/>
-      <c r="L10" s="177" t="inlineStr"/>
+      <c r="L10" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M10" s="177" t="inlineStr"/>
     </row>
     <row r="11">
@@ -4495,9 +4567,17 @@
           <t>403</t>
         </is>
       </c>
-      <c r="J11" s="177" t="inlineStr"/>
+      <c r="J11" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K11" s="177" t="inlineStr"/>
-      <c r="L11" s="177" t="inlineStr"/>
+      <c r="L11" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M11" s="177" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4542,9 +4622,17 @@
           <t>403 Lead-tier required</t>
         </is>
       </c>
-      <c r="J12" s="177" t="inlineStr"/>
+      <c r="J12" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K12" s="177" t="inlineStr"/>
-      <c r="L12" s="177" t="inlineStr"/>
+      <c r="L12" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.5s)</t>
+        </is>
+      </c>
       <c r="M12" s="177" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4589,9 +4677,17 @@
           <t>400 validation error</t>
         </is>
       </c>
-      <c r="J13" s="177" t="inlineStr"/>
+      <c r="J13" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K13" s="177" t="inlineStr"/>
-      <c r="L13" s="177" t="inlineStr"/>
+      <c r="L13" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M13" s="177" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4636,9 +4732,17 @@
           <t>403 segregation of duties</t>
         </is>
       </c>
-      <c r="J14" s="177" t="inlineStr"/>
+      <c r="J14" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K14" s="177" t="inlineStr"/>
-      <c r="L14" s="177" t="inlineStr"/>
+      <c r="L14" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.6s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M14" s="177" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4683,9 +4787,17 @@
           <t>409 - only approved can be returned to FA</t>
         </is>
       </c>
-      <c r="J15" s="177" t="inlineStr"/>
+      <c r="J15" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K15" s="177" t="inlineStr"/>
-      <c r="L15" s="177" t="inlineStr"/>
+      <c r="L15" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M15" s="177" t="inlineStr"/>
     </row>
     <row r="16">
@@ -4730,9 +4842,17 @@
           <t>409</t>
         </is>
       </c>
-      <c r="J16" s="177" t="inlineStr"/>
+      <c r="J16" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K16" s="177" t="inlineStr"/>
-      <c r="L16" s="177" t="inlineStr"/>
+      <c r="L16" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.8s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.7s)</t>
+        </is>
+      </c>
       <c r="M16" s="177" t="inlineStr"/>
     </row>
     <row r="17">
@@ -4777,9 +4897,17 @@
           <t>409 must be approved first</t>
         </is>
       </c>
-      <c r="J17" s="177" t="inlineStr"/>
+      <c r="J17" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K17" s="177" t="inlineStr"/>
-      <c r="L17" s="177" t="inlineStr"/>
+      <c r="L17" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M17" s="177" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4824,9 +4952,17 @@
           <t>403</t>
         </is>
       </c>
-      <c r="J18" s="177" t="inlineStr"/>
+      <c r="J18" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K18" s="177" t="inlineStr"/>
-      <c r="L18" s="177" t="inlineStr"/>
+      <c r="L18" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.4s)</t>
+        </is>
+      </c>
       <c r="M18" s="177" t="inlineStr"/>
     </row>
     <row r="19">
@@ -4871,9 +5007,17 @@
           <t>Edit restricted</t>
         </is>
       </c>
-      <c r="J19" s="177" t="inlineStr"/>
+      <c r="J19" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K19" s="177" t="inlineStr"/>
-      <c r="L19" s="177" t="inlineStr"/>
+      <c r="L19" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.4s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.4s)</t>
+        </is>
+      </c>
       <c r="M19" s="177" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4918,9 +5062,17 @@
           <t>Exactly one local defect (23505 caught); no twin</t>
         </is>
       </c>
-      <c r="J20" s="177" t="inlineStr"/>
+      <c r="J20" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K20" s="177" t="inlineStr"/>
-      <c r="L20" s="177" t="inlineStr"/>
+      <c r="L20" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Failed (0.1s) — Error: second register → 500 || Last automated run: 2026-07-19 03:22 UTC — Passed (0.4s)</t>
+        </is>
+      </c>
       <c r="M20" s="177" t="inlineStr"/>
     </row>
     <row r="21">
@@ -4965,9 +5117,17 @@
           <t>400 unknown status</t>
         </is>
       </c>
-      <c r="J21" s="177" t="inlineStr"/>
+      <c r="J21" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K21" s="177" t="inlineStr"/>
-      <c r="L21" s="177" t="inlineStr"/>
+      <c r="L21" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.7s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M21" s="177" t="inlineStr"/>
     </row>
     <row r="22">
@@ -5012,9 +5172,17 @@
           <t>400/404 (no 500)</t>
         </is>
       </c>
-      <c r="J22" s="177" t="inlineStr"/>
+      <c r="J22" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K22" s="177" t="inlineStr"/>
-      <c r="L22" s="177" t="inlineStr"/>
+      <c r="L22" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M22" s="177" t="inlineStr"/>
     </row>
     <row r="23">
@@ -5059,9 +5227,17 @@
           <t>400 projectId must be an integer</t>
         </is>
       </c>
-      <c r="J23" s="177" t="inlineStr"/>
+      <c r="J23" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K23" s="177" t="inlineStr"/>
-      <c r="L23" s="177" t="inlineStr"/>
+      <c r="L23" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M23" s="177" t="inlineStr"/>
     </row>
     <row r="24">
@@ -5106,9 +5282,17 @@
           <t>409 conflict</t>
         </is>
       </c>
-      <c r="J24" s="177" t="inlineStr"/>
+      <c r="J24" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K24" s="177" t="inlineStr"/>
-      <c r="L24" s="177" t="inlineStr"/>
+      <c r="L24" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M24" s="177" t="inlineStr"/>
     </row>
     <row r="25">
@@ -5153,9 +5337,17 @@
           <t>400</t>
         </is>
       </c>
-      <c r="J25" s="177" t="inlineStr"/>
+      <c r="J25" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K25" s="177" t="inlineStr"/>
-      <c r="L25" s="177" t="inlineStr"/>
+      <c r="L25" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M25" s="177" t="inlineStr"/>
     </row>
     <row r="26">
@@ -5200,9 +5392,17 @@
           <t>400 - must be one of ENV1-ENV6</t>
         </is>
       </c>
-      <c r="J26" s="177" t="inlineStr"/>
+      <c r="J26" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K26" s="177" t="inlineStr"/>
-      <c r="L26" s="177" t="inlineStr"/>
+      <c r="L26" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M26" s="177" t="inlineStr"/>
     </row>
     <row r="27">
@@ -5247,9 +5447,17 @@
           <t>400 - module isn't on this project</t>
         </is>
       </c>
-      <c r="J27" s="177" t="inlineStr"/>
+      <c r="J27" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K27" s="177" t="inlineStr"/>
-      <c r="L27" s="177" t="inlineStr"/>
+      <c r="L27" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.2s)</t>
+        </is>
+      </c>
       <c r="M27" s="177" t="inlineStr"/>
     </row>
     <row r="28">
@@ -5294,9 +5502,17 @@
           <t>403</t>
         </is>
       </c>
-      <c r="J28" s="177" t="inlineStr"/>
+      <c r="J28" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K28" s="177" t="inlineStr"/>
-      <c r="L28" s="177" t="inlineStr"/>
+      <c r="L28" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.1s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M28" s="177" t="inlineStr"/>
     </row>
     <row r="29">
@@ -5342,9 +5558,17 @@
           <t>I do NOT receive my own action's notification</t>
         </is>
       </c>
-      <c r="J29" s="177" t="inlineStr"/>
+      <c r="J29" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K29" s="177" t="inlineStr"/>
-      <c r="L29" s="177" t="inlineStr"/>
+      <c r="L29" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (3.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (3.2s)</t>
+        </is>
+      </c>
       <c r="M29" s="177" t="inlineStr"/>
     </row>
     <row r="30">
@@ -5389,9 +5613,17 @@
           <t>Module-A-only FA is NOT notified for module-B review</t>
         </is>
       </c>
-      <c r="J30" s="177" t="inlineStr"/>
+      <c r="J30" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K30" s="177" t="inlineStr"/>
-      <c r="L30" s="177" t="inlineStr"/>
+      <c r="L30" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (3.8s) || Last automated run: 2026-07-19 03:22 UTC — Passed (3.9s)</t>
+        </is>
+      </c>
       <c r="M30" s="177" t="inlineStr"/>
     </row>
     <row r="31">
@@ -5436,9 +5668,17 @@
           <t>Rejected with a clear limit error</t>
         </is>
       </c>
-      <c r="J31" s="177" t="inlineStr"/>
+      <c r="J31" s="177" t="inlineStr">
+        <is>
+          <t>Not Executed</t>
+        </is>
+      </c>
       <c r="K31" s="177" t="inlineStr"/>
-      <c r="L31" s="177" t="inlineStr"/>
+      <c r="L31" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Not Executed (0.0s) || Last automated run: 2026-07-19 03:22 UTC — Not Executed (0.0s)</t>
+        </is>
+      </c>
       <c r="M31" s="177" t="inlineStr"/>
     </row>
     <row r="32">
@@ -5484,9 +5724,17 @@
           <t>Handled gracefully (accepted/truncated/validated - no crash)</t>
         </is>
       </c>
-      <c r="J32" s="177" t="inlineStr"/>
+      <c r="J32" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K32" s="177" t="inlineStr"/>
-      <c r="L32" s="177" t="inlineStr"/>
+      <c r="L32" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.2s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.1s)</t>
+        </is>
+      </c>
       <c r="M32" s="177" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5531,9 +5779,17 @@
           <t>Requirement shows as uncovered (0 TCs) - not hidden</t>
         </is>
       </c>
-      <c r="J33" s="177" t="inlineStr"/>
+      <c r="J33" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K33" s="177" t="inlineStr"/>
-      <c r="L33" s="177" t="inlineStr"/>
+      <c r="L33" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.7s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.7s)</t>
+        </is>
+      </c>
       <c r="M33" s="177" t="inlineStr"/>
     </row>
     <row r="34">
@@ -5579,9 +5835,17 @@
           <t>No-op; dirty indicator stays clean; no spurious history entry</t>
         </is>
       </c>
-      <c r="J34" s="177" t="inlineStr"/>
+      <c r="J34" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K34" s="177" t="inlineStr"/>
-      <c r="L34" s="177" t="inlineStr"/>
+      <c r="L34" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.3s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.3s)</t>
+        </is>
+      </c>
       <c r="M34" s="177" t="inlineStr"/>
     </row>
     <row r="35">
@@ -5626,9 +5890,17 @@
           <t>Defect inherits the file's milestoneId (shows in escape funnel)</t>
         </is>
       </c>
-      <c r="J35" s="177" t="inlineStr"/>
+      <c r="J35" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K35" s="177" t="inlineStr"/>
-      <c r="L35" s="177" t="inlineStr"/>
+      <c r="L35" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.5s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.6s)</t>
+        </is>
+      </c>
       <c r="M35" s="177" t="inlineStr"/>
     </row>
     <row r="36">
@@ -5674,9 +5946,17 @@
           <t>Member falls back to whole-project (not zero records)</t>
         </is>
       </c>
-      <c r="J36" s="177" t="inlineStr"/>
+      <c r="J36" s="177" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
       <c r="K36" s="177" t="inlineStr"/>
-      <c r="L36" s="177" t="inlineStr"/>
+      <c r="L36" s="177" t="inlineStr">
+        <is>
+          <t>Last automated run: 2026-07-19 03:01 UTC — Passed (0.8s) || Last automated run: 2026-07-19 03:22 UTC — Passed (0.8s)</t>
+        </is>
+      </c>
       <c r="M36" s="177" t="inlineStr"/>
     </row>
   </sheetData>
